--- a/data/trans_orig/IP09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66256</t>
+          <t>66047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65593</t>
+          <t>65240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50363</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>30014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>41459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74915</t>
+          <t>74653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>91615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>110749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132825</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21692</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>22704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26876</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>20027</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39047</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55646</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63483</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82662</t>
+          <t>82067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91363</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3431</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6936</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5903</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7223</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7218</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6936</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9009</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16061</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10629</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21372</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8013</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4496</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4333</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12256</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16061</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11273</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21835</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37380</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32069</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42812</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22547</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18104</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26064</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18304</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26227</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37380</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31606</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42168</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>52931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>66050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>53441</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>53441</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>53441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2873</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4550</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7963</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -1527,67 +1527,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>15120</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11776</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17706</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>14993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11444</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17220</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11723</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17233</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15120</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11707</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17730</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17866</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>17866</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>17866</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18092</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30739</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18927</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18237</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31815</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59436</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52739</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65386</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43443</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37316</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48008</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38006</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>48176</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>59436</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>51663</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>65240</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93497</t>
+          <t>93525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>110455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>56243</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9391</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5355</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8383</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8281</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9401</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7391</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4363</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4465</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>57,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7805</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22883</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16717</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29328</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18961</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13424</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24869</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13752</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24944</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22883</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17080</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30285</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47512</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41067</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53678</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35922</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30014</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41459</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29939</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>41131</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47512</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>53315</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74653</t>
+          <t>75220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91615</t>
+          <t>92490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54883</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54883</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54883</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>70395</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>70395</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>70395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4422</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8671</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4081</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7338</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16052</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11803</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18358</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11159</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7902</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13292</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7609</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>16052</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12098</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18520</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26680</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43680</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22023</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35934</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21589</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35499</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26828</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>42523</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>74753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68167</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58739</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>54472</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46935</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60846</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>61280</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>68167</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>59896</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>75591</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110749</t>
+          <t>110536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132095</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82869</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3285</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3049</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,68%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16745</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11753</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21841</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13259</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8976</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17717</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8955</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17772</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>42,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16745</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11823</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21933</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>43,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21770</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16674</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26762</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17818</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13360</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22101</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13305</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22122</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21770</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>16582</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>56,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4418</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7393</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7212</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8193</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7179</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9587</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4385</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9692</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4607</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7272</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18195</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29911</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>58,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13995</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24775</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13988</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24681</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51558</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33252</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28046</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22348</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33128</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22442</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33135</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27672</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21710</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>33423</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>63233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6740</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9069</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4485</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7099</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2642</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7662</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17186</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10098</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25019</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7541</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16780</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40707</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34408</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49329</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24778</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20027</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29266</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55645</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>57625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82067</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36807</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36807</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>36807</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>102624</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102624</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102624</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5316</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2237</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9089</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2405</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8713</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14463</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17542</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11461</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7880</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14188</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>30364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17739</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36240</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17052</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35165</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61189</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71132</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>38881</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27617</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45730</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>61,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>33335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>108309</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121835</t>
+          <t>110966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
